--- a/docs/content_history/pbr-2026-vm20-table-j-swaps.xlsx
+++ b/docs/content_history/pbr-2026-vm20-table-j-swaps.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\PBR\VM20_VM22_ProductSupport\PBR Production Web Data\Current Year\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0154C389-F2B5-45E1-AC30-CE3A57ABA9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9676CA6-9403-4054-A6A3-9DD17EDDCE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="January_2026" sheetId="29" r:id="rId1"/>
-    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId2"/>
-    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId3"/>
+    <sheet name="February_2026" sheetId="30" r:id="rId1"/>
+    <sheet name="January_2026" sheetId="29" r:id="rId2"/>
+    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId3"/>
+    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
   <si>
     <t>Weighted</t>
   </si>
@@ -65,6 +66,9 @@
   </si>
   <si>
     <t>** The  3 and 6 Month Current SOFR Swap Spreads are based on Term SOFR Rates obtained by contract from the CME Group.  The market data and all rights in and to it are the property of Chicago Mercantile Exchange Inc. or its licensors as applicable. All rights reserved, except as expressly licensed by Chicago Mercantile Exchange Inc.</t>
+  </si>
+  <si>
+    <t>Table J (02/27/2026) Swap Benchmark Spreads (in bps)</t>
   </si>
 </sst>
 </file>
@@ -147,7 +151,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -174,6 +178,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1617,21 +1622,432 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C73779D-48E1-4396-BCEC-CC77B9A96BB8}">
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="3" width="19.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6">
+        <v>6.6479016953999999</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-8.4250997040000009</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6">
+        <v>7.1046583332999997</v>
+      </c>
+      <c r="C5" s="6">
+        <v>-18.93440395</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6">
+        <v>-2.926712974</v>
+      </c>
+      <c r="C6" s="6">
+        <v>-6.5887610170000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6">
+        <v>-14.054845930000001</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-9.7081414230000007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6">
+        <v>-19.05586533</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-13.98810675</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6">
+        <v>-21.562719229999999</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-18.163567799999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6">
+        <v>-24.50846623</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-21.174162429999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6">
+        <v>-29.26293536</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-23.611543269999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6">
+        <v>-33.452144599999997</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-25.245948890000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6">
+        <v>-36.257550690000002</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-26.324832099999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6">
+        <v>-38.687743159999997</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-27.1029667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6">
+        <v>-40.57952607</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-27.763705009999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6">
+        <v>-43.304706379999999</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-28.626325300000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="5">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6">
+        <v>-47.412468269999998</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-29.829543770000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6">
+        <v>-51.459958409999999</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-31.411004590000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="5">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6">
+        <v>-54.779237950000002</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-33.229500090000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6">
+        <v>-57.657033689999999</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-35.198334799999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6">
+        <v>-60.051196099999999</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-37.274791999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="5">
+        <v>17</v>
+      </c>
+      <c r="B22" s="6">
+        <v>-61.971416550000001</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-39.409508690000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="5">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6">
+        <v>-63.46370709</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-41.543833069999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="5">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6">
+        <v>-64.639361570000005</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-43.618617270000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="5">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6">
+        <v>-65.546315149999998</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-45.574980590000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="5">
+        <v>21</v>
+      </c>
+      <c r="B26" s="6">
+        <v>-66.269236430000007</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-47.448015589999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="5">
+        <v>22</v>
+      </c>
+      <c r="B27" s="6">
+        <v>-66.873256389999995</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-49.245376489999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="5">
+        <v>23</v>
+      </c>
+      <c r="B28" s="6">
+        <v>-67.405144989999997</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-50.88986045</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6">
+        <v>-67.899962639999998</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-52.317818180000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="5">
+        <v>25</v>
+      </c>
+      <c r="B30" s="6">
+        <v>-68.393121019999995</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-53.46845055</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="5">
+        <v>26</v>
+      </c>
+      <c r="B31" s="6">
+        <v>-68.919188009999999</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-54.307336859999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="5">
+        <v>27</v>
+      </c>
+      <c r="B32" s="6">
+        <v>-69.427228479999997</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-54.84603224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="5">
+        <v>28</v>
+      </c>
+      <c r="B33" s="6">
+        <v>-69.967548239999999</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-55.085355589999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="5">
+        <v>29</v>
+      </c>
+      <c r="B34" s="6">
+        <v>-70.560267899999999</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-55.022050309999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="5">
+        <v>30</v>
+      </c>
+      <c r="B35" s="6">
+        <v>-71.285762520000006</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-54.69621807</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="8">
+        <v>-46.996314603915621</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-35.002318548249995</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="10"/>
+    </row>
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F39390C-8944-4BA3-A374-C71CF55A3914}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.7109375" customWidth="1"/>
+    <col min="1" max="3" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +2058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1653,7 +2069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1664,7 +2080,7 @@
         <v>-8.4643284360000006</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -1675,7 +2091,7 @@
         <v>-18.986706460000001</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -1686,7 +2102,7 @@
         <v>-6.606153613</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
@@ -1697,7 +2113,7 @@
         <v>-9.6725825039999993</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
@@ -1708,7 +2124,7 @@
         <v>-13.90377076</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
@@ -1719,7 +2135,7 @@
         <v>-18.05126491</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
@@ -1730,7 +2146,7 @@
         <v>-21.058171550000001</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
@@ -1741,7 +2157,7 @@
         <v>-23.482340529999998</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
@@ -1752,7 +2168,7 @@
         <v>-25.112373340000001</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
@@ -1763,7 +2179,7 @@
         <v>-26.207170059999999</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
@@ -1774,7 +2190,7 @@
         <v>-27.01171896</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
@@ -1785,7 +2201,7 @@
         <v>-27.699147780000001</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
@@ -1796,7 +2212,7 @@
         <v>-28.582440519999999</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
@@ -1807,7 +2223,7 @@
         <v>-29.797805400000001</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
@@ -1818,7 +2234,7 @@
         <v>-31.38552271</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
@@ -1829,7 +2245,7 @@
         <v>-33.206359569999996</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
@@ -1840,7 +2256,7 @@
         <v>-35.175185190000001</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
@@ -1851,7 +2267,7 @@
         <v>-37.250174440000002</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
@@ -1862,7 +2278,7 @@
         <v>-39.383293340000002</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
@@ -1873,7 +2289,7 @@
         <v>-41.514898170000002</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
@@ -1884,7 +2300,7 @@
         <v>-43.58589877</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
@@ -1895,7 +2311,7 @@
         <v>-45.536655600000003</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
@@ -1906,7 +2322,7 @@
         <v>-47.402761550000001</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
@@ -1917,7 +2333,7 @@
         <v>-49.193163900000002</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
@@ -1928,7 +2344,7 @@
         <v>-50.831508980000002</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
@@ -1939,7 +2355,7 @@
         <v>-52.254304140000002</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
@@ -1950,7 +2366,7 @@
         <v>-53.401048920000001</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
@@ -1961,7 +2377,7 @@
         <v>-54.237701129999998</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
@@ -1972,7 +2388,7 @@
         <v>-54.776711149999997</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
@@ -1983,7 +2399,7 @@
         <v>-55.018984750000001</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
@@ -1994,7 +2410,7 @@
         <v>-54.961556510000001</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
@@ -2005,7 +2421,7 @@
         <v>-54.64476792</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
@@ -2016,12 +2432,12 @@
         <v>-34.949889736343749</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>10</v>
       </c>
@@ -2038,28 +2454,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25262A5-84B2-4BF6-AF4E-DBAA1AC8379B}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="H31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="31" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H31" s="1"/>
     </row>
   </sheetData>

--- a/docs/content_history/pbr-2026-vm20-table-j-swaps.xlsx
+++ b/docs/content_history/pbr-2026-vm20-table-j-swaps.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\PBR\VM20_VM22_ProductSupport\PBR Production Web Data\Current Year\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9676CA6-9403-4054-A6A3-9DD17EDDCE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDA1737-2E36-4B74-A647-B25735806B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37320" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="February_2026" sheetId="30" r:id="rId1"/>
-    <sheet name="January_2026" sheetId="29" r:id="rId2"/>
-    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId3"/>
-    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId4"/>
+    <sheet name="March_2026" sheetId="31" r:id="rId1"/>
+    <sheet name="February_2026" sheetId="30" r:id="rId2"/>
+    <sheet name="January_2026" sheetId="29" r:id="rId3"/>
+    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId4"/>
+    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="13">
   <si>
     <t>Weighted</t>
   </si>
@@ -69,6 +70,9 @@
   </si>
   <si>
     <t>Table J (02/27/2026) Swap Benchmark Spreads (in bps)</t>
+  </si>
+  <si>
+    <t>Table J (03/31/2026) Swap Benchmark Spreads (in bps)</t>
   </si>
 </sst>
 </file>
@@ -175,10 +179,10 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1301,7 +1305,7 @@
                   <a14:compatExt spid="_x0000_s4104"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000008100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000008100000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1622,6 +1626,417 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F94775C-2142-4275-87E7-127A4B3F5670}">
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="3" width="19.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6">
+        <v>5.3375646118000004</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-8.3424564629999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6">
+        <v>3.3978625</v>
+      </c>
+      <c r="C5" s="6">
+        <v>-18.777869509999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6">
+        <v>5.5674684034000004</v>
+      </c>
+      <c r="C6" s="6">
+        <v>-6.5031848160000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6">
+        <v>-13.537172590000001</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-9.7470649100000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6">
+        <v>-19.83186422</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-14.10108906</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6">
+        <v>-23.69107455</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-18.311611160000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6">
+        <v>-26.914938200000002</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-21.32924062</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6">
+        <v>-32.255423810000003</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-23.789757460000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6">
+        <v>-36.193182800000002</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-25.435076939999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6">
+        <v>-38.412868670000002</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-26.49993439</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6">
+        <v>-39.806424229999998</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-27.253286039999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6">
+        <v>-41.173835609999998</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-27.88923986</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6">
+        <v>-43.806296109999998</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-28.740374060000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="5">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6">
+        <v>-47.875078430000002</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-29.947605299999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6">
+        <v>-52.311473079999999</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-31.540475489999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="5">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6">
+        <v>-56.34412116</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-33.370618149999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6">
+        <v>-59.867190520000001</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-35.350059170000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6">
+        <v>-62.880936679999998</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-37.43498262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="5">
+        <v>17</v>
+      </c>
+      <c r="B22" s="6">
+        <v>-65.361396940000006</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-39.575345630000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="5">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6">
+        <v>-67.330193910000006</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-41.712729410000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="5">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6">
+        <v>-68.757097520000002</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-43.789159099999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="5">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6">
+        <v>-69.771599120000005</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-45.74685538</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="5">
+        <v>21</v>
+      </c>
+      <c r="B26" s="6">
+        <v>-70.410478620000006</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-47.620851180000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="5">
+        <v>22</v>
+      </c>
+      <c r="B27" s="6">
+        <v>-70.858830580000003</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-49.418218719999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="5">
+        <v>23</v>
+      </c>
+      <c r="B28" s="6">
+        <v>-71.148167659999999</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-51.06233443</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6">
+        <v>-71.408914379999999</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-52.489967970000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="5">
+        <v>25</v>
+      </c>
+      <c r="B30" s="6">
+        <v>-71.603900089999996</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-53.640615599999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="5">
+        <v>26</v>
+      </c>
+      <c r="B31" s="6">
+        <v>-71.800155090000004</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-54.479416669999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="5">
+        <v>27</v>
+      </c>
+      <c r="B32" s="6">
+        <v>-72.009803989999995</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-55.017806149999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="5">
+        <v>28</v>
+      </c>
+      <c r="B33" s="6">
+        <v>-72.24265149</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-55.256465159999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="5">
+        <v>29</v>
+      </c>
+      <c r="B34" s="6">
+        <v>-72.558470569999997</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-55.192006220000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="5">
+        <v>30</v>
+      </c>
+      <c r="B35" s="6">
+        <v>-72.989332079999997</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-54.864078890000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="8">
+        <v>-49.026561787025003</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-35.132180516531243</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="9"/>
+    </row>
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C73779D-48E1-4396-BCEC-CC77B9A96BB8}">
   <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2022,17 +2437,17 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="10"/>
+      <c r="A38" s="9"/>
     </row>
     <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="10"/>
+      <c r="A39" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F39390C-8944-4BA3-A374-C71CF55A3914}">
   <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2438,13 +2853,13 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2454,7 +2869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25262A5-84B2-4BF6-AF4E-DBAA1AC8379B}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFFFFF00"/>
@@ -2467,7 +2882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFFFFF00"/>

--- a/docs/content_history/pbr-2026-vm20-table-j-swaps.xlsx
+++ b/docs/content_history/pbr-2026-vm20-table-j-swaps.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\PBR\VM20_VM22_ProductSupport\PBR Production Web Data\Current Year\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDA1737-2E36-4B74-A647-B25735806B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94BAD6A-3B4B-4310-BBE3-FB9F88347D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37320" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="March_2026" sheetId="31" r:id="rId1"/>
-    <sheet name="February_2026" sheetId="30" r:id="rId2"/>
-    <sheet name="January_2026" sheetId="29" r:id="rId3"/>
-    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId4"/>
-    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId5"/>
+    <sheet name="April_2026" sheetId="32" r:id="rId1"/>
+    <sheet name="March_2026" sheetId="31" r:id="rId2"/>
+    <sheet name="February_2026" sheetId="30" r:id="rId3"/>
+    <sheet name="January_2026" sheetId="29" r:id="rId4"/>
+    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId5"/>
+    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="14">
   <si>
     <t>Weighted</t>
   </si>
@@ -73,6 +74,9 @@
   </si>
   <si>
     <t>Table J (03/31/2026) Swap Benchmark Spreads (in bps)</t>
+  </si>
+  <si>
+    <t>Table J (04/30/2026) Swap Benchmark Spreads (in bps)</t>
   </si>
 </sst>
 </file>
@@ -1305,7 +1309,7 @@
                   <a14:compatExt spid="_x0000_s4104"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000008100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000008100000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1626,21 +1630,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F94775C-2142-4275-87E7-127A4B3F5670}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE08ECD6-E0B3-47D7-BDA1-FF8CF79629C2}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="19.6328125" customWidth="1"/>
+    <col min="1" max="3" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1651,7 +1655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1662,373 +1666,373 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="6">
-        <v>5.3375646118000004</v>
+        <v>5.4656270949000003</v>
       </c>
       <c r="C4" s="7">
-        <v>-8.3424564629999995</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-8.2776989360000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="6">
-        <v>3.3978625</v>
+        <v>2.7917770833</v>
       </c>
       <c r="C5" s="6">
-        <v>-18.777869509999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-18.637616690000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>5.5674684034000004</v>
+        <v>3.2522290633000002</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.5031848160000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-6.4232812399999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-13.537172590000001</v>
+        <v>-13.76739341</v>
       </c>
       <c r="C7" s="6">
-        <v>-9.7470649100000006</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-9.7789523450000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-19.83186422</v>
+        <v>-19.639277369999999</v>
       </c>
       <c r="C8" s="6">
-        <v>-14.10108906</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-14.19343054</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-23.69107455</v>
+        <v>-23.840411499999998</v>
       </c>
       <c r="C9" s="6">
-        <v>-18.311611160000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-18.431195979999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-26.914938200000002</v>
+        <v>-27.674485140000002</v>
       </c>
       <c r="C10" s="6">
-        <v>-21.32924062</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-21.45117243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-32.255423810000003</v>
+        <v>-32.600308210000001</v>
       </c>
       <c r="C11" s="6">
-        <v>-23.789757460000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-23.925118130000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-36.193182800000002</v>
+        <v>-36.604923210000003</v>
       </c>
       <c r="C12" s="6">
-        <v>-25.435076939999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-25.573245150000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-38.412868670000002</v>
+        <v>-39.272860889999997</v>
       </c>
       <c r="C13" s="6">
-        <v>-26.49993439</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-26.619840060000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-39.806424229999998</v>
+        <v>-41.311656620000001</v>
       </c>
       <c r="C14" s="6">
-        <v>-27.253286039999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-27.34710553</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-41.173835609999998</v>
+        <v>-43.201924329999997</v>
       </c>
       <c r="C15" s="6">
-        <v>-27.88923986</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-27.958789509999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-43.806296109999998</v>
+        <v>-46.106159210000001</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.740374060000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-28.798412549999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-47.875078430000002</v>
+        <v>-50.35169234</v>
       </c>
       <c r="C17" s="6">
-        <v>-29.947605299999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-30.00817378</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-52.311473079999999</v>
+        <v>-54.850820880000001</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.540475489999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-31.61033583</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-56.34412116</v>
+        <v>-58.854156760000002</v>
       </c>
       <c r="C19" s="6">
-        <v>-33.370618149999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-33.451087039999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-59.867190520000001</v>
+        <v>-62.247379870000003</v>
       </c>
       <c r="C20" s="6">
-        <v>-35.350059170000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-35.440966639999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-62.880936679999998</v>
+        <v>-65.238530260000005</v>
       </c>
       <c r="C21" s="6">
-        <v>-37.43498262</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-37.53497617</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-65.361396940000006</v>
+        <v>-67.625832919999993</v>
       </c>
       <c r="C22" s="6">
-        <v>-39.575345630000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-39.682454610000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-67.330193910000006</v>
+        <v>-69.530889540000004</v>
       </c>
       <c r="C23" s="6">
-        <v>-41.712729410000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-41.82489374</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-68.757097520000002</v>
+        <v>-70.919225139999995</v>
       </c>
       <c r="C24" s="6">
-        <v>-43.789159099999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-43.905581509999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-69.771599120000005</v>
+        <v>-71.944191549999999</v>
       </c>
       <c r="C25" s="6">
-        <v>-45.74685538</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-45.867936219999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-70.410478620000006</v>
+        <v>-72.571375349999997</v>
       </c>
       <c r="C26" s="6">
-        <v>-47.620851180000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-47.746305820000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-70.858830580000003</v>
+        <v>-73.076964770000004</v>
       </c>
       <c r="C27" s="6">
-        <v>-49.418218719999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-49.546995160000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-71.148167659999999</v>
+        <v>-73.489324640000007</v>
       </c>
       <c r="C28" s="6">
-        <v>-51.06233443</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-51.193317739999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-71.408914379999999</v>
+        <v>-73.821622860000005</v>
       </c>
       <c r="C29" s="6">
-        <v>-52.489967970000002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-52.622764349999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-71.603900089999996</v>
+        <v>-74.097566240000006</v>
       </c>
       <c r="C30" s="6">
-        <v>-53.640615599999997</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-53.774887589999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-71.800155090000004</v>
+        <v>-74.38676298</v>
       </c>
       <c r="C31" s="6">
-        <v>-54.479416669999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-54.61396491</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-72.009803989999995</v>
+        <v>-74.618037220000005</v>
       </c>
       <c r="C32" s="6">
-        <v>-55.017806149999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-55.15135282</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-72.24265149</v>
+        <v>-74.939932659999997</v>
       </c>
       <c r="C33" s="6">
-        <v>-55.256465159999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-55.387617259999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-72.558470569999997</v>
+        <v>-75.282139909999998</v>
       </c>
       <c r="C34" s="6">
-        <v>-55.192006220000003</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-55.318991519999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-72.989332079999997</v>
+        <v>-75.772571650000003</v>
       </c>
       <c r="C35" s="6">
-        <v>-54.864078890000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-54.985567879999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="8">
-        <v>-49.026561787025003</v>
+        <v>-50.816524505890627</v>
       </c>
       <c r="C36" s="8">
-        <v>-35.132180516531243</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-35.221375927531248</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="9"/>
     </row>
-    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9"/>
     </row>
   </sheetData>
@@ -2037,21 +2041,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C73779D-48E1-4396-BCEC-CC77B9A96BB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F94775C-2142-4275-87E7-127A4B3F5670}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="19.6328125" customWidth="1"/>
+    <col min="1" max="3" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2062,7 +2066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2073,373 +2077,373 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="6">
-        <v>6.6479016953999999</v>
+        <v>5.3375646118000004</v>
       </c>
       <c r="C4" s="7">
-        <v>-8.4250997040000009</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-8.3424564629999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="6">
-        <v>7.1046583332999997</v>
+        <v>3.3978625</v>
       </c>
       <c r="C5" s="6">
-        <v>-18.93440395</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-18.777869509999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>-2.926712974</v>
+        <v>5.5674684034000004</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.5887610170000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-6.5031848160000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-14.054845930000001</v>
+        <v>-13.537172590000001</v>
       </c>
       <c r="C7" s="6">
-        <v>-9.7081414230000007</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-9.7470649100000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-19.05586533</v>
+        <v>-19.83186422</v>
       </c>
       <c r="C8" s="6">
-        <v>-13.98810675</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-14.10108906</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-21.562719229999999</v>
+        <v>-23.69107455</v>
       </c>
       <c r="C9" s="6">
-        <v>-18.163567799999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-18.311611160000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-24.50846623</v>
+        <v>-26.914938200000002</v>
       </c>
       <c r="C10" s="6">
-        <v>-21.174162429999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-21.32924062</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-29.26293536</v>
+        <v>-32.255423810000003</v>
       </c>
       <c r="C11" s="6">
-        <v>-23.611543269999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-23.789757460000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-33.452144599999997</v>
+        <v>-36.193182800000002</v>
       </c>
       <c r="C12" s="6">
-        <v>-25.245948890000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-25.435076939999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-36.257550690000002</v>
+        <v>-38.412868670000002</v>
       </c>
       <c r="C13" s="6">
-        <v>-26.324832099999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-26.49993439</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-38.687743159999997</v>
+        <v>-39.806424229999998</v>
       </c>
       <c r="C14" s="6">
-        <v>-27.1029667</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-27.253286039999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-40.57952607</v>
+        <v>-41.173835609999998</v>
       </c>
       <c r="C15" s="6">
-        <v>-27.763705009999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-27.88923986</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-43.304706379999999</v>
+        <v>-43.806296109999998</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.626325300000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-28.740374060000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-47.412468269999998</v>
+        <v>-47.875078430000002</v>
       </c>
       <c r="C17" s="6">
-        <v>-29.829543770000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-29.947605299999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-51.459958409999999</v>
+        <v>-52.311473079999999</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.411004590000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-31.540475489999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-54.779237950000002</v>
+        <v>-56.34412116</v>
       </c>
       <c r="C19" s="6">
-        <v>-33.229500090000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-33.370618149999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-57.657033689999999</v>
+        <v>-59.867190520000001</v>
       </c>
       <c r="C20" s="6">
-        <v>-35.198334799999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-35.350059170000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-60.051196099999999</v>
+        <v>-62.880936679999998</v>
       </c>
       <c r="C21" s="6">
-        <v>-37.274791999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-37.43498262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-61.971416550000001</v>
+        <v>-65.361396940000006</v>
       </c>
       <c r="C22" s="6">
-        <v>-39.409508690000003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-39.575345630000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-63.46370709</v>
+        <v>-67.330193910000006</v>
       </c>
       <c r="C23" s="6">
-        <v>-41.543833069999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-41.712729410000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-64.639361570000005</v>
+        <v>-68.757097520000002</v>
       </c>
       <c r="C24" s="6">
-        <v>-43.618617270000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-43.789159099999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-65.546315149999998</v>
+        <v>-69.771599120000005</v>
       </c>
       <c r="C25" s="6">
-        <v>-45.574980590000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-45.74685538</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-66.269236430000007</v>
+        <v>-70.410478620000006</v>
       </c>
       <c r="C26" s="6">
-        <v>-47.448015589999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-47.620851180000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-66.873256389999995</v>
+        <v>-70.858830580000003</v>
       </c>
       <c r="C27" s="6">
-        <v>-49.245376489999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-49.418218719999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-67.405144989999997</v>
+        <v>-71.148167659999999</v>
       </c>
       <c r="C28" s="6">
-        <v>-50.88986045</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-51.06233443</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-67.899962639999998</v>
+        <v>-71.408914379999999</v>
       </c>
       <c r="C29" s="6">
-        <v>-52.317818180000003</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-52.489967970000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-68.393121019999995</v>
+        <v>-71.603900089999996</v>
       </c>
       <c r="C30" s="6">
-        <v>-53.46845055</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-53.640615599999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-68.919188009999999</v>
+        <v>-71.800155090000004</v>
       </c>
       <c r="C31" s="6">
-        <v>-54.307336859999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-54.479416669999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-69.427228479999997</v>
+        <v>-72.009803989999995</v>
       </c>
       <c r="C32" s="6">
-        <v>-54.84603224</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-55.017806149999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-69.967548239999999</v>
+        <v>-72.24265149</v>
       </c>
       <c r="C33" s="6">
-        <v>-55.085355589999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-55.256465159999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-70.560267899999999</v>
+        <v>-72.558470569999997</v>
       </c>
       <c r="C34" s="6">
-        <v>-55.022050309999997</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-55.192006220000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-71.285762520000006</v>
+        <v>-72.989332079999997</v>
       </c>
       <c r="C35" s="6">
-        <v>-54.69621807</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-54.864078890000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="8">
-        <v>-46.996314603915621</v>
+        <v>-49.026561787025003</v>
       </c>
       <c r="C36" s="8">
-        <v>-35.002318548249995</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-35.132180516531243</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="9"/>
     </row>
-    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9"/>
     </row>
   </sheetData>
@@ -2448,21 +2452,432 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C73779D-48E1-4396-BCEC-CC77B9A96BB8}">
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="19.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6">
+        <v>6.6479016953999999</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-8.4250997040000009</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6">
+        <v>7.1046583332999997</v>
+      </c>
+      <c r="C5" s="6">
+        <v>-18.93440395</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6">
+        <v>-2.926712974</v>
+      </c>
+      <c r="C6" s="6">
+        <v>-6.5887610170000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6">
+        <v>-14.054845930000001</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-9.7081414230000007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6">
+        <v>-19.05586533</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-13.98810675</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6">
+        <v>-21.562719229999999</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-18.163567799999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6">
+        <v>-24.50846623</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-21.174162429999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6">
+        <v>-29.26293536</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-23.611543269999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6">
+        <v>-33.452144599999997</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-25.245948890000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6">
+        <v>-36.257550690000002</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-26.324832099999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6">
+        <v>-38.687743159999997</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-27.1029667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6">
+        <v>-40.57952607</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-27.763705009999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6">
+        <v>-43.304706379999999</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-28.626325300000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6">
+        <v>-47.412468269999998</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-29.829543770000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6">
+        <v>-51.459958409999999</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-31.411004590000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6">
+        <v>-54.779237950000002</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-33.229500090000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6">
+        <v>-57.657033689999999</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-35.198334799999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6">
+        <v>-60.051196099999999</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-37.274791999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>17</v>
+      </c>
+      <c r="B22" s="6">
+        <v>-61.971416550000001</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-39.409508690000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6">
+        <v>-63.46370709</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-41.543833069999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6">
+        <v>-64.639361570000005</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-43.618617270000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6">
+        <v>-65.546315149999998</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-45.574980590000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>21</v>
+      </c>
+      <c r="B26" s="6">
+        <v>-66.269236430000007</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-47.448015589999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>22</v>
+      </c>
+      <c r="B27" s="6">
+        <v>-66.873256389999995</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-49.245376489999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>23</v>
+      </c>
+      <c r="B28" s="6">
+        <v>-67.405144989999997</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-50.88986045</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6">
+        <v>-67.899962639999998</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-52.317818180000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>25</v>
+      </c>
+      <c r="B30" s="6">
+        <v>-68.393121019999995</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-53.46845055</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>26</v>
+      </c>
+      <c r="B31" s="6">
+        <v>-68.919188009999999</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-54.307336859999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>27</v>
+      </c>
+      <c r="B32" s="6">
+        <v>-69.427228479999997</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-54.84603224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>28</v>
+      </c>
+      <c r="B33" s="6">
+        <v>-69.967548239999999</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-55.085355589999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>29</v>
+      </c>
+      <c r="B34" s="6">
+        <v>-70.560267899999999</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-55.022050309999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>30</v>
+      </c>
+      <c r="B35" s="6">
+        <v>-71.285762520000006</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-54.69621807</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="8">
+        <v>-46.996314603915621</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-35.002318548249995</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+    </row>
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F39390C-8944-4BA3-A374-C71CF55A3914}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="19.7265625" customWidth="1"/>
+    <col min="1" max="3" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2473,7 +2888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2484,7 +2899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -2495,7 +2910,7 @@
         <v>-8.4643284360000006</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -2506,7 +2921,7 @@
         <v>-18.986706460000001</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -2517,7 +2932,7 @@
         <v>-6.606153613</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>2</v>
       </c>
@@ -2528,7 +2943,7 @@
         <v>-9.6725825039999993</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>3</v>
       </c>
@@ -2539,7 +2954,7 @@
         <v>-13.90377076</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>4</v>
       </c>
@@ -2550,7 +2965,7 @@
         <v>-18.05126491</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>5</v>
       </c>
@@ -2561,7 +2976,7 @@
         <v>-21.058171550000001</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>6</v>
       </c>
@@ -2572,7 +2987,7 @@
         <v>-23.482340529999998</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>7</v>
       </c>
@@ -2583,7 +2998,7 @@
         <v>-25.112373340000001</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>8</v>
       </c>
@@ -2594,7 +3009,7 @@
         <v>-26.207170059999999</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>9</v>
       </c>
@@ -2605,7 +3020,7 @@
         <v>-27.01171896</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>10</v>
       </c>
@@ -2616,7 +3031,7 @@
         <v>-27.699147780000001</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>11</v>
       </c>
@@ -2627,7 +3042,7 @@
         <v>-28.582440519999999</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>12</v>
       </c>
@@ -2638,7 +3053,7 @@
         <v>-29.797805400000001</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>13</v>
       </c>
@@ -2649,7 +3064,7 @@
         <v>-31.38552271</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>14</v>
       </c>
@@ -2660,7 +3075,7 @@
         <v>-33.206359569999996</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>15</v>
       </c>
@@ -2671,7 +3086,7 @@
         <v>-35.175185190000001</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>16</v>
       </c>
@@ -2682,7 +3097,7 @@
         <v>-37.250174440000002</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>17</v>
       </c>
@@ -2693,7 +3108,7 @@
         <v>-39.383293340000002</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>18</v>
       </c>
@@ -2704,7 +3119,7 @@
         <v>-41.514898170000002</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>19</v>
       </c>
@@ -2715,7 +3130,7 @@
         <v>-43.58589877</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>20</v>
       </c>
@@ -2726,7 +3141,7 @@
         <v>-45.536655600000003</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>21</v>
       </c>
@@ -2737,7 +3152,7 @@
         <v>-47.402761550000001</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>22</v>
       </c>
@@ -2748,7 +3163,7 @@
         <v>-49.193163900000002</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>23</v>
       </c>
@@ -2759,7 +3174,7 @@
         <v>-50.831508980000002</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>24</v>
       </c>
@@ -2770,7 +3185,7 @@
         <v>-52.254304140000002</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>25</v>
       </c>
@@ -2781,7 +3196,7 @@
         <v>-53.401048920000001</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>26</v>
       </c>
@@ -2792,7 +3207,7 @@
         <v>-54.237701129999998</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>27</v>
       </c>
@@ -2803,7 +3218,7 @@
         <v>-54.776711149999997</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>28</v>
       </c>
@@ -2814,7 +3229,7 @@
         <v>-55.018984750000001</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>29</v>
       </c>
@@ -2825,7 +3240,7 @@
         <v>-54.961556510000001</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>30</v>
       </c>
@@ -2836,7 +3251,7 @@
         <v>-54.64476792</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
@@ -2847,12 +3262,12 @@
         <v>-34.949889736343749</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>10</v>
       </c>
@@ -2869,28 +3284,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25262A5-84B2-4BF6-AF4E-DBAA1AC8379B}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="H31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="31" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H31" s="1"/>
     </row>
   </sheetData>

--- a/docs/content_history/pbr-2026-vm20-table-j-swaps.xlsx
+++ b/docs/content_history/pbr-2026-vm20-table-j-swaps.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\PBR\VM20_VM22_ProductSupport\PBR Production Web Data\Current Year\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94BAD6A-3B4B-4310-BBE3-FB9F88347D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4349E50B-610D-4337-BF0C-E721DF9CE25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="April_2026" sheetId="32" r:id="rId1"/>
-    <sheet name="March_2026" sheetId="31" r:id="rId2"/>
-    <sheet name="February_2026" sheetId="30" r:id="rId3"/>
-    <sheet name="January_2026" sheetId="29" r:id="rId4"/>
-    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId5"/>
-    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId6"/>
+    <sheet name="May_2026" sheetId="33" r:id="rId1"/>
+    <sheet name="April_2026" sheetId="32" r:id="rId2"/>
+    <sheet name="March_2026" sheetId="31" r:id="rId3"/>
+    <sheet name="February_2026" sheetId="30" r:id="rId4"/>
+    <sheet name="January_2026" sheetId="29" r:id="rId5"/>
+    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId6"/>
+    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="15">
   <si>
     <t>Weighted</t>
   </si>
@@ -77,6 +78,9 @@
   </si>
   <si>
     <t>Table J (04/30/2026) Swap Benchmark Spreads (in bps)</t>
+  </si>
+  <si>
+    <t>Table J (05/29/2026) Swap Benchmark Spreads (in bps)</t>
   </si>
 </sst>
 </file>
@@ -1309,7 +1313,7 @@
                   <a14:compatExt spid="_x0000_s4104"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000008100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000008100000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1630,6 +1634,417 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D72FD6-E7CE-48C2-B800-0D5FB4C78145}">
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="19.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6">
+        <v>3.7908085643999998</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-8.261432997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6">
+        <v>-1.199983333</v>
+      </c>
+      <c r="C5" s="6">
+        <v>-18.569600250000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6">
+        <v>6.0748948512999998</v>
+      </c>
+      <c r="C6" s="6">
+        <v>-6.4037058949999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6">
+        <v>-8.6309275210000003</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-9.8316411949999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6">
+        <v>-17.674616530000002</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-14.30136051</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6">
+        <v>-21.864437460000001</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-18.564622450000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6">
+        <v>-23.157085250000002</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-21.58750723</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6">
+        <v>-27.25490332</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-24.066500699999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6">
+        <v>-30.955399759999999</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-25.708170020000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6">
+        <v>-33.693737210000002</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-26.732405279999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6">
+        <v>-36.080411959999999</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-27.43084198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6">
+        <v>-38.133838160000003</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-28.014819809999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6">
+        <v>-41.170119059999998</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-28.835615650000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6">
+        <v>-45.505789460000003</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-30.037594739999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6">
+        <v>-49.990685130000003</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-31.6401796</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6">
+        <v>-53.882441999999998</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-33.48489017</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6">
+        <v>-57.191209389999997</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-35.481676409999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6">
+        <v>-60.070490470000003</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-37.583403359999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>17</v>
+      </c>
+      <c r="B22" s="6">
+        <v>-62.37442987</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-39.738181660000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6">
+        <v>-64.148812860000007</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-41.887459120000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6">
+        <v>-65.500366380000003</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-43.975171250000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6">
+        <v>-66.495458229999997</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-45.945323270000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>21</v>
+      </c>
+      <c r="B26" s="6">
+        <v>-67.139445749999993</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-47.832018320000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>22</v>
+      </c>
+      <c r="B27" s="6">
+        <v>-67.679059429999995</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-49.639557500000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>23</v>
+      </c>
+      <c r="B28" s="6">
+        <v>-68.089006879999999</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-51.291055180000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6">
+        <v>-68.492318229999995</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-52.723801950000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>25</v>
+      </c>
+      <c r="B30" s="6">
+        <v>-68.84406353</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-53.877128859999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>26</v>
+      </c>
+      <c r="B31" s="6">
+        <v>-69.160419640000001</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-54.714570199999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>27</v>
+      </c>
+      <c r="B32" s="6">
+        <v>-69.471355040000006</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-55.247039729999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>28</v>
+      </c>
+      <c r="B33" s="6">
+        <v>-69.822986599999993</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-55.474978409999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>29</v>
+      </c>
+      <c r="B34" s="6">
+        <v>-70.208273520000006</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-55.394471189999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>30</v>
+      </c>
+      <c r="B35" s="6">
+        <v>-70.740176829999996</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-55.045291089999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="8">
+        <v>-46.39864204338437</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-35.291312999281253</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+    </row>
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE08ECD6-E0B3-47D7-BDA1-FF8CF79629C2}">
   <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2040,7 +2455,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F94775C-2142-4275-87E7-127A4B3F5670}">
   <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2451,7 +2866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C73779D-48E1-4396-BCEC-CC77B9A96BB8}">
   <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2862,7 +3277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F39390C-8944-4BA3-A374-C71CF55A3914}">
   <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3284,7 +3699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25262A5-84B2-4BF6-AF4E-DBAA1AC8379B}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFFFFF00"/>
@@ -3297,7 +3712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFFFFF00"/>

--- a/docs/content_history/pbr-2026-vm20-table-j-swaps.xlsx
+++ b/docs/content_history/pbr-2026-vm20-table-j-swaps.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\PBR\VM20_VM22_ProductSupport\PBR Production Web Data\Current Year\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4349E50B-610D-4337-BF0C-E721DF9CE25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067321BE-F3D5-453F-A4B5-130437CA5258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="May_2026" sheetId="33" r:id="rId1"/>
-    <sheet name="April_2026" sheetId="32" r:id="rId2"/>
-    <sheet name="March_2026" sheetId="31" r:id="rId3"/>
-    <sheet name="February_2026" sheetId="30" r:id="rId4"/>
-    <sheet name="January_2026" sheetId="29" r:id="rId5"/>
-    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId6"/>
-    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId7"/>
+    <sheet name="June_2026" sheetId="34" r:id="rId1"/>
+    <sheet name="May_2026" sheetId="33" r:id="rId2"/>
+    <sheet name="April_2026" sheetId="32" r:id="rId3"/>
+    <sheet name="March_2026" sheetId="31" r:id="rId4"/>
+    <sheet name="February_2026" sheetId="30" r:id="rId5"/>
+    <sheet name="January_2026" sheetId="29" r:id="rId6"/>
+    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId7"/>
+    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="16">
   <si>
     <t>Weighted</t>
   </si>
@@ -81,6 +82,9 @@
   </si>
   <si>
     <t>Table J (05/29/2026) Swap Benchmark Spreads (in bps)</t>
+  </si>
+  <si>
+    <t>Table J (06/30/2026) Swap Benchmark Spreads (in bps)</t>
   </si>
 </sst>
 </file>
@@ -1313,7 +1317,7 @@
                   <a14:compatExt spid="_x0000_s4104"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000008100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000008100000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1634,6 +1638,417 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECEBD057-EA7C-4F62-BF98-7479884C6DE0}">
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="19.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6">
+        <v>-6.389212594</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-8.2313927289999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6">
+        <v>-10.446291670000001</v>
+      </c>
+      <c r="C5" s="6">
+        <v>-18.51192713</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6">
+        <v>5.7397921384000004</v>
+      </c>
+      <c r="C6" s="6">
+        <v>-6.4096345980000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6">
+        <v>-11.303101939999999</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-9.9134916109999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6">
+        <v>-17.918094320000002</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-14.43123391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6">
+        <v>-22.253412640000001</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-18.72422014</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6">
+        <v>-25.629521350000001</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-21.76219553</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6">
+        <v>-30.047948000000002</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-24.251589370000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6">
+        <v>-33.724754840000003</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-25.88581392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6">
+        <v>-36.18146033</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-26.88485627</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6">
+        <v>-38.116209550000001</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-27.549867750000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6">
+        <v>-39.798883689999997</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-28.100707629999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6">
+        <v>-42.695726049999998</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-28.895933119999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6">
+        <v>-46.849379980000002</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-30.084057229999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6">
+        <v>-51.282258550000002</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-31.682138299999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6">
+        <v>-55.33608392</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-33.52710373</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6">
+        <v>-58.811453659999998</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-35.527590529999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6">
+        <v>-61.704858440000002</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-37.634295420000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>17</v>
+      </c>
+      <c r="B22" s="6">
+        <v>-64.001455750000005</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-39.794160720000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6">
+        <v>-65.743557350000003</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-41.948185770000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6">
+        <v>-67.039155289999997</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-44.041218960000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6">
+        <v>-67.877724459999996</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-46.017685970000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>21</v>
+      </c>
+      <c r="B26" s="6">
+        <v>-68.380490120000005</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-47.911377369999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>22</v>
+      </c>
+      <c r="B27" s="6">
+        <v>-68.721968770000004</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-49.724284840000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>23</v>
+      </c>
+      <c r="B28" s="6">
+        <v>-68.987308069999997</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-51.379822570000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6">
+        <v>-69.192030340000002</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-52.814546059999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>25</v>
+      </c>
+      <c r="B30" s="6">
+        <v>-69.389554709999999</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-53.967732779999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>26</v>
+      </c>
+      <c r="B31" s="6">
+        <v>-69.519314789999996</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-54.802068599999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>27</v>
+      </c>
+      <c r="B32" s="6">
+        <v>-69.652903159999994</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-55.328075570000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>28</v>
+      </c>
+      <c r="B33" s="6">
+        <v>-69.793760719999995</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-55.546003480000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>29</v>
+      </c>
+      <c r="B34" s="6">
+        <v>-70.063770820000002</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-55.451850659999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>30</v>
+      </c>
+      <c r="B35" s="6">
+        <v>-70.398083549999996</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-55.08526045</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="8">
+        <v>-48.172185540174993</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-35.369385084937505</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+    </row>
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D72FD6-E7CE-48C2-B800-0D5FB4C78145}">
   <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2044,7 +2459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE08ECD6-E0B3-47D7-BDA1-FF8CF79629C2}">
   <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2455,7 +2870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F94775C-2142-4275-87E7-127A4B3F5670}">
   <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2866,7 +3281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C73779D-48E1-4396-BCEC-CC77B9A96BB8}">
   <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3277,7 +3692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F39390C-8944-4BA3-A374-C71CF55A3914}">
   <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3699,7 +4114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25262A5-84B2-4BF6-AF4E-DBAA1AC8379B}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFFFFF00"/>
@@ -3712,7 +4127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFFFFF00"/>

--- a/docs/content_history/pbr-2026-vm20-table-j-swaps.xlsx
+++ b/docs/content_history/pbr-2026-vm20-table-j-swaps.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\PBR\VM20_VM22_ProductSupport\PBR Production Web Data\Current Year\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067321BE-F3D5-453F-A4B5-130437CA5258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F9463E-869B-48F6-9BE3-3AE4AB1C4EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" tabRatio="795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="June_2026" sheetId="34" r:id="rId1"/>
-    <sheet name="May_2026" sheetId="33" r:id="rId2"/>
-    <sheet name="April_2026" sheetId="32" r:id="rId3"/>
-    <sheet name="March_2026" sheetId="31" r:id="rId4"/>
-    <sheet name="February_2026" sheetId="30" r:id="rId5"/>
-    <sheet name="January_2026" sheetId="29" r:id="rId6"/>
-    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId7"/>
-    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId8"/>
+    <sheet name="July_2026" sheetId="35" r:id="rId1"/>
+    <sheet name="June_2026" sheetId="34" r:id="rId2"/>
+    <sheet name="May_2026" sheetId="33" r:id="rId3"/>
+    <sheet name="April_2026" sheetId="32" r:id="rId4"/>
+    <sheet name="March_2026" sheetId="31" r:id="rId5"/>
+    <sheet name="February_2026" sheetId="30" r:id="rId6"/>
+    <sheet name="January_2026" sheetId="29" r:id="rId7"/>
+    <sheet name="LIBOR to SOFR Disclosure" sheetId="16" r:id="rId8"/>
+    <sheet name="LEGAL DISCLAIMER" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="17">
   <si>
     <t>Weighted</t>
   </si>
@@ -85,6 +86,9 @@
   </si>
   <si>
     <t>Table J (06/30/2026) Swap Benchmark Spreads (in bps)</t>
+  </si>
+  <si>
+    <t>Table J (07/31/2026) Swap Benchmark Spreads (in bps)</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1321,7 @@
                   <a14:compatExt spid="_x0000_s4104"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000008100000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000008100000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1638,21 +1642,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECEBD057-EA7C-4F62-BF98-7479884C6DE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BF1A1B-0D5A-4C40-A616-555031A58FA8}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.7109375" customWidth="1"/>
+    <col min="1" max="3" width="19.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1663,7 +1667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1674,373 +1678,373 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="6">
-        <v>-6.389212594</v>
+        <v>-0.62756451300000005</v>
       </c>
       <c r="C4" s="7">
-        <v>-8.2313927289999995</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.1726383830000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="6">
-        <v>-10.446291670000001</v>
+        <v>-4.5831375000000003</v>
       </c>
       <c r="C5" s="6">
-        <v>-18.51192713</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-18.412061250000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>5.7397921384000004</v>
+        <v>3.0902227761000001</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.4096345980000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-6.3692469340000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-11.303101939999999</v>
+        <v>-11.353027640000001</v>
       </c>
       <c r="C7" s="6">
-        <v>-9.9134916109999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-9.9945046620000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-17.918094320000002</v>
+        <v>-17.334729450000001</v>
       </c>
       <c r="C8" s="6">
-        <v>-14.43123391</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-14.574310179999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-22.253412640000001</v>
+        <v>-22.345368610000001</v>
       </c>
       <c r="C9" s="6">
-        <v>-18.72422014</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-18.907064290000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-25.629521350000001</v>
+        <v>-26.647618739999999</v>
       </c>
       <c r="C10" s="6">
-        <v>-21.76219553</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-21.959026900000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-30.047948000000002</v>
+        <v>-31.246773690000001</v>
       </c>
       <c r="C11" s="6">
-        <v>-24.251589370000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-24.460817389999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-33.724754840000003</v>
+        <v>-35.049929689999999</v>
       </c>
       <c r="C12" s="6">
-        <v>-25.88581392</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-26.08714453</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-36.18146033</v>
+        <v>-37.581207480000003</v>
       </c>
       <c r="C13" s="6">
-        <v>-26.88485627</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.056553539999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-38.116209550000001</v>
+        <v>-39.48039902</v>
       </c>
       <c r="C14" s="6">
-        <v>-27.549867750000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.683461510000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-39.798883689999997</v>
+        <v>-41.284781719999998</v>
       </c>
       <c r="C15" s="6">
-        <v>-28.100707629999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.199670449999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-42.695726049999998</v>
+        <v>-44.262449840000002</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.895933119999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.97599417</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-46.849379980000002</v>
+        <v>-48.697835449999999</v>
       </c>
       <c r="C17" s="6">
-        <v>-30.084057229999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-30.161928929999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-51.282258550000002</v>
+        <v>-53.401627689999998</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.682138299999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-31.766016759999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-55.33608392</v>
+        <v>-57.563670000000002</v>
       </c>
       <c r="C19" s="6">
-        <v>-33.52710373</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-33.618183289999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-58.811453659999998</v>
+        <v>-61.187050910000004</v>
       </c>
       <c r="C20" s="6">
-        <v>-35.527590529999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.626310680000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-61.704858440000002</v>
+        <v>-64.236642309999993</v>
       </c>
       <c r="C21" s="6">
-        <v>-37.634295420000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-37.739177259999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-64.001455750000005</v>
+        <v>-66.715323420000004</v>
       </c>
       <c r="C22" s="6">
-        <v>-39.794160720000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-39.902633770000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-65.743557350000003</v>
+        <v>-68.660867479999993</v>
       </c>
       <c r="C23" s="6">
-        <v>-41.948185770000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-42.057867549999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-67.039155289999997</v>
+        <v>-70.081757890000006</v>
       </c>
       <c r="C24" s="6">
-        <v>-44.041218960000002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-44.15115892</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-67.877724459999996</v>
+        <v>-71.025658160000006</v>
       </c>
       <c r="C25" s="6">
-        <v>-46.017685970000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-46.127897849999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-68.380490120000005</v>
+        <v>-71.672638030000002</v>
       </c>
       <c r="C26" s="6">
-        <v>-47.911377369999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-48.021691580000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-68.721968770000004</v>
+        <v>-72.080930050000006</v>
       </c>
       <c r="C27" s="6">
-        <v>-49.724284840000003</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-49.833445930000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-68.987308069999997</v>
+        <v>-72.397865440000004</v>
       </c>
       <c r="C28" s="6">
-        <v>-51.379822570000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-51.486940330000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-69.192030340000002</v>
+        <v>-72.6502251</v>
       </c>
       <c r="C29" s="6">
-        <v>-52.814546059999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-52.918751729999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-69.389554709999999</v>
+        <v>-72.845179160000001</v>
       </c>
       <c r="C30" s="6">
-        <v>-53.967732779999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-54.068651080000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-69.519314789999996</v>
+        <v>-73.072066579999998</v>
       </c>
       <c r="C31" s="6">
-        <v>-54.802068599999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-54.898645369999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-69.652903159999994</v>
+        <v>-73.247245559999996</v>
       </c>
       <c r="C32" s="6">
-        <v>-55.328075570000003</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.419183099999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-69.793760719999995</v>
+        <v>-73.509900060000007</v>
       </c>
       <c r="C33" s="6">
-        <v>-55.546003480000003</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.630098670000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-70.063770820000002</v>
+        <v>-73.857212739999994</v>
       </c>
       <c r="C34" s="6">
-        <v>-55.451850659999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.527671980000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-70.398083549999996</v>
+        <v>-74.248641860000006</v>
       </c>
       <c r="C35" s="6">
-        <v>-55.08526045</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.151127529999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="8">
-        <v>-48.172185540174993</v>
+        <v>-49.995596968965629</v>
       </c>
       <c r="C36" s="8">
-        <v>-35.369385084937505</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.467496140593752</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
     </row>
-    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
     </row>
   </sheetData>
@@ -2049,21 +2053,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D72FD6-E7CE-48C2-B800-0D5FB4C78145}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECEBD057-EA7C-4F62-BF98-7479884C6DE0}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.7109375" customWidth="1"/>
+    <col min="1" max="3" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2074,7 +2078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2085,373 +2089,373 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="6">
-        <v>3.7908085643999998</v>
+        <v>-6.389212594</v>
       </c>
       <c r="C4" s="7">
-        <v>-8.261432997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.2313927289999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="6">
-        <v>-1.199983333</v>
+        <v>-10.446291670000001</v>
       </c>
       <c r="C5" s="6">
-        <v>-18.569600250000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-18.51192713</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>6.0748948512999998</v>
+        <v>5.7397921384000004</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.4037058949999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-6.4096345980000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-8.6309275210000003</v>
+        <v>-11.303101939999999</v>
       </c>
       <c r="C7" s="6">
-        <v>-9.8316411949999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-9.9134916109999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-17.674616530000002</v>
+        <v>-17.918094320000002</v>
       </c>
       <c r="C8" s="6">
-        <v>-14.30136051</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-14.43123391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-21.864437460000001</v>
+        <v>-22.253412640000001</v>
       </c>
       <c r="C9" s="6">
-        <v>-18.564622450000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-18.72422014</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-23.157085250000002</v>
+        <v>-25.629521350000001</v>
       </c>
       <c r="C10" s="6">
-        <v>-21.58750723</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-21.76219553</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-27.25490332</v>
+        <v>-30.047948000000002</v>
       </c>
       <c r="C11" s="6">
-        <v>-24.066500699999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-24.251589370000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-30.955399759999999</v>
+        <v>-33.724754840000003</v>
       </c>
       <c r="C12" s="6">
-        <v>-25.708170020000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-25.88581392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-33.693737210000002</v>
+        <v>-36.18146033</v>
       </c>
       <c r="C13" s="6">
-        <v>-26.732405279999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-26.88485627</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-36.080411959999999</v>
+        <v>-38.116209550000001</v>
       </c>
       <c r="C14" s="6">
-        <v>-27.43084198</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.549867750000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-38.133838160000003</v>
+        <v>-39.798883689999997</v>
       </c>
       <c r="C15" s="6">
-        <v>-28.014819809999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.100707629999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-41.170119059999998</v>
+        <v>-42.695726049999998</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.835615650000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.895933119999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-45.505789460000003</v>
+        <v>-46.849379980000002</v>
       </c>
       <c r="C17" s="6">
-        <v>-30.037594739999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-30.084057229999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-49.990685130000003</v>
+        <v>-51.282258550000002</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.6401796</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-31.682138299999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-53.882441999999998</v>
+        <v>-55.33608392</v>
       </c>
       <c r="C19" s="6">
-        <v>-33.48489017</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-33.52710373</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-57.191209389999997</v>
+        <v>-58.811453659999998</v>
       </c>
       <c r="C20" s="6">
-        <v>-35.481676409999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.527590529999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-60.070490470000003</v>
+        <v>-61.704858440000002</v>
       </c>
       <c r="C21" s="6">
-        <v>-37.583403359999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-37.634295420000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-62.37442987</v>
+        <v>-64.001455750000005</v>
       </c>
       <c r="C22" s="6">
-        <v>-39.738181660000002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-39.794160720000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-64.148812860000007</v>
+        <v>-65.743557350000003</v>
       </c>
       <c r="C23" s="6">
-        <v>-41.887459120000003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-41.948185770000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-65.500366380000003</v>
+        <v>-67.039155289999997</v>
       </c>
       <c r="C24" s="6">
-        <v>-43.975171250000002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-44.041218960000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-66.495458229999997</v>
+        <v>-67.877724459999996</v>
       </c>
       <c r="C25" s="6">
-        <v>-45.945323270000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-46.017685970000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-67.139445749999993</v>
+        <v>-68.380490120000005</v>
       </c>
       <c r="C26" s="6">
-        <v>-47.832018320000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-47.911377369999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-67.679059429999995</v>
+        <v>-68.721968770000004</v>
       </c>
       <c r="C27" s="6">
-        <v>-49.639557500000002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-49.724284840000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-68.089006879999999</v>
+        <v>-68.987308069999997</v>
       </c>
       <c r="C28" s="6">
-        <v>-51.291055180000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-51.379822570000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-68.492318229999995</v>
+        <v>-69.192030340000002</v>
       </c>
       <c r="C29" s="6">
-        <v>-52.723801950000002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-52.814546059999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-68.84406353</v>
+        <v>-69.389554709999999</v>
       </c>
       <c r="C30" s="6">
-        <v>-53.877128859999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-53.967732779999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-69.160419640000001</v>
+        <v>-69.519314789999996</v>
       </c>
       <c r="C31" s="6">
-        <v>-54.714570199999997</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-54.802068599999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-69.471355040000006</v>
+        <v>-69.652903159999994</v>
       </c>
       <c r="C32" s="6">
-        <v>-55.247039729999997</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.328075570000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-69.822986599999993</v>
+        <v>-69.793760719999995</v>
       </c>
       <c r="C33" s="6">
-        <v>-55.474978409999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.546003480000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-70.208273520000006</v>
+        <v>-70.063770820000002</v>
       </c>
       <c r="C34" s="6">
-        <v>-55.394471189999997</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.451850659999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-70.740176829999996</v>
+        <v>-70.398083549999996</v>
       </c>
       <c r="C35" s="6">
-        <v>-55.045291089999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.08526045</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="8">
-        <v>-46.39864204338437</v>
+        <v>-48.172185540174993</v>
       </c>
       <c r="C36" s="8">
-        <v>-35.291312999281253</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.369385084937505</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
     </row>
-    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
     </row>
   </sheetData>
@@ -2460,21 +2464,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE08ECD6-E0B3-47D7-BDA1-FF8CF79629C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D72FD6-E7CE-48C2-B800-0D5FB4C78145}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.7109375" customWidth="1"/>
+    <col min="1" max="3" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2485,7 +2489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2496,373 +2500,373 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="6">
-        <v>5.4656270949000003</v>
+        <v>3.7908085643999998</v>
       </c>
       <c r="C4" s="7">
-        <v>-8.2776989360000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.261432997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="6">
-        <v>2.7917770833</v>
+        <v>-1.199983333</v>
       </c>
       <c r="C5" s="6">
-        <v>-18.637616690000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-18.569600250000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>3.2522290633000002</v>
+        <v>6.0748948512999998</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.4232812399999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-6.4037058949999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-13.76739341</v>
+        <v>-8.6309275210000003</v>
       </c>
       <c r="C7" s="6">
-        <v>-9.7789523450000004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-9.8316411949999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-19.639277369999999</v>
+        <v>-17.674616530000002</v>
       </c>
       <c r="C8" s="6">
-        <v>-14.19343054</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-14.30136051</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-23.840411499999998</v>
+        <v>-21.864437460000001</v>
       </c>
       <c r="C9" s="6">
-        <v>-18.431195979999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-18.564622450000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-27.674485140000002</v>
+        <v>-23.157085250000002</v>
       </c>
       <c r="C10" s="6">
-        <v>-21.45117243</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-21.58750723</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-32.600308210000001</v>
+        <v>-27.25490332</v>
       </c>
       <c r="C11" s="6">
-        <v>-23.925118130000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-24.066500699999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-36.604923210000003</v>
+        <v>-30.955399759999999</v>
       </c>
       <c r="C12" s="6">
-        <v>-25.573245150000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-25.708170020000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-39.272860889999997</v>
+        <v>-33.693737210000002</v>
       </c>
       <c r="C13" s="6">
-        <v>-26.619840060000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-26.732405279999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-41.311656620000001</v>
+        <v>-36.080411959999999</v>
       </c>
       <c r="C14" s="6">
-        <v>-27.34710553</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.43084198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-43.201924329999997</v>
+        <v>-38.133838160000003</v>
       </c>
       <c r="C15" s="6">
-        <v>-27.958789509999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.014819809999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-46.106159210000001</v>
+        <v>-41.170119059999998</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.798412549999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.835615650000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-50.35169234</v>
+        <v>-45.505789460000003</v>
       </c>
       <c r="C17" s="6">
-        <v>-30.00817378</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-30.037594739999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-54.850820880000001</v>
+        <v>-49.990685130000003</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.61033583</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-31.6401796</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-58.854156760000002</v>
+        <v>-53.882441999999998</v>
       </c>
       <c r="C19" s="6">
-        <v>-33.451087039999997</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-33.48489017</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-62.247379870000003</v>
+        <v>-57.191209389999997</v>
       </c>
       <c r="C20" s="6">
-        <v>-35.440966639999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.481676409999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-65.238530260000005</v>
+        <v>-60.070490470000003</v>
       </c>
       <c r="C21" s="6">
-        <v>-37.53497617</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-37.583403359999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-67.625832919999993</v>
+        <v>-62.37442987</v>
       </c>
       <c r="C22" s="6">
-        <v>-39.682454610000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-39.738181660000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-69.530889540000004</v>
+        <v>-64.148812860000007</v>
       </c>
       <c r="C23" s="6">
-        <v>-41.82489374</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-41.887459120000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-70.919225139999995</v>
+        <v>-65.500366380000003</v>
       </c>
       <c r="C24" s="6">
-        <v>-43.905581509999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-43.975171250000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-71.944191549999999</v>
+        <v>-66.495458229999997</v>
       </c>
       <c r="C25" s="6">
-        <v>-45.867936219999997</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-45.945323270000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-72.571375349999997</v>
+        <v>-67.139445749999993</v>
       </c>
       <c r="C26" s="6">
-        <v>-47.746305820000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-47.832018320000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-73.076964770000004</v>
+        <v>-67.679059429999995</v>
       </c>
       <c r="C27" s="6">
-        <v>-49.546995160000002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-49.639557500000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-73.489324640000007</v>
+        <v>-68.089006879999999</v>
       </c>
       <c r="C28" s="6">
-        <v>-51.193317739999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-51.291055180000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-73.821622860000005</v>
+        <v>-68.492318229999995</v>
       </c>
       <c r="C29" s="6">
-        <v>-52.622764349999997</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-52.723801950000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-74.097566240000006</v>
+        <v>-68.84406353</v>
       </c>
       <c r="C30" s="6">
-        <v>-53.774887589999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-53.877128859999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-74.38676298</v>
+        <v>-69.160419640000001</v>
       </c>
       <c r="C31" s="6">
-        <v>-54.61396491</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-54.714570199999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-74.618037220000005</v>
+        <v>-69.471355040000006</v>
       </c>
       <c r="C32" s="6">
-        <v>-55.15135282</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.247039729999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-74.939932659999997</v>
+        <v>-69.822986599999993</v>
       </c>
       <c r="C33" s="6">
-        <v>-55.387617259999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.474978409999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-75.282139909999998</v>
+        <v>-70.208273520000006</v>
       </c>
       <c r="C34" s="6">
-        <v>-55.318991519999997</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.394471189999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-75.772571650000003</v>
+        <v>-70.740176829999996</v>
       </c>
       <c r="C35" s="6">
-        <v>-54.985567879999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.045291089999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="8">
-        <v>-50.816524505890627</v>
+        <v>-46.39864204338437</v>
       </c>
       <c r="C36" s="8">
-        <v>-35.221375927531248</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.291312999281253</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
     </row>
-    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
     </row>
   </sheetData>
@@ -2871,21 +2875,21 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F94775C-2142-4275-87E7-127A4B3F5670}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE08ECD6-E0B3-47D7-BDA1-FF8CF79629C2}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.5703125" customWidth="1"/>
+    <col min="1" max="3" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2896,7 +2900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2907,373 +2911,373 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="6">
-        <v>5.3375646118000004</v>
+        <v>5.4656270949000003</v>
       </c>
       <c r="C4" s="7">
-        <v>-8.3424564629999995</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.2776989360000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="6">
-        <v>3.3978625</v>
+        <v>2.7917770833</v>
       </c>
       <c r="C5" s="6">
-        <v>-18.777869509999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-18.637616690000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>5.5674684034000004</v>
+        <v>3.2522290633000002</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.5031848160000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-6.4232812399999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-13.537172590000001</v>
+        <v>-13.76739341</v>
       </c>
       <c r="C7" s="6">
-        <v>-9.7470649100000006</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-9.7789523450000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-19.83186422</v>
+        <v>-19.639277369999999</v>
       </c>
       <c r="C8" s="6">
-        <v>-14.10108906</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-14.19343054</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-23.69107455</v>
+        <v>-23.840411499999998</v>
       </c>
       <c r="C9" s="6">
-        <v>-18.311611160000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-18.431195979999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-26.914938200000002</v>
+        <v>-27.674485140000002</v>
       </c>
       <c r="C10" s="6">
-        <v>-21.32924062</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-21.45117243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-32.255423810000003</v>
+        <v>-32.600308210000001</v>
       </c>
       <c r="C11" s="6">
-        <v>-23.789757460000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-23.925118130000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-36.193182800000002</v>
+        <v>-36.604923210000003</v>
       </c>
       <c r="C12" s="6">
-        <v>-25.435076939999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-25.573245150000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-38.412868670000002</v>
+        <v>-39.272860889999997</v>
       </c>
       <c r="C13" s="6">
-        <v>-26.49993439</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-26.619840060000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-39.806424229999998</v>
+        <v>-41.311656620000001</v>
       </c>
       <c r="C14" s="6">
-        <v>-27.253286039999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.34710553</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-41.173835609999998</v>
+        <v>-43.201924329999997</v>
       </c>
       <c r="C15" s="6">
-        <v>-27.88923986</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.958789509999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-43.806296109999998</v>
+        <v>-46.106159210000001</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.740374060000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.798412549999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-47.875078430000002</v>
+        <v>-50.35169234</v>
       </c>
       <c r="C17" s="6">
-        <v>-29.947605299999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-30.00817378</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-52.311473079999999</v>
+        <v>-54.850820880000001</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.540475489999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-31.61033583</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-56.34412116</v>
+        <v>-58.854156760000002</v>
       </c>
       <c r="C19" s="6">
-        <v>-33.370618149999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-33.451087039999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-59.867190520000001</v>
+        <v>-62.247379870000003</v>
       </c>
       <c r="C20" s="6">
-        <v>-35.350059170000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.440966639999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-62.880936679999998</v>
+        <v>-65.238530260000005</v>
       </c>
       <c r="C21" s="6">
-        <v>-37.43498262</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-37.53497617</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-65.361396940000006</v>
+        <v>-67.625832919999993</v>
       </c>
       <c r="C22" s="6">
-        <v>-39.575345630000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-39.682454610000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-67.330193910000006</v>
+        <v>-69.530889540000004</v>
       </c>
       <c r="C23" s="6">
-        <v>-41.712729410000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-41.82489374</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-68.757097520000002</v>
+        <v>-70.919225139999995</v>
       </c>
       <c r="C24" s="6">
-        <v>-43.789159099999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-43.905581509999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-69.771599120000005</v>
+        <v>-71.944191549999999</v>
       </c>
       <c r="C25" s="6">
-        <v>-45.74685538</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-45.867936219999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-70.410478620000006</v>
+        <v>-72.571375349999997</v>
       </c>
       <c r="C26" s="6">
-        <v>-47.620851180000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-47.746305820000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-70.858830580000003</v>
+        <v>-73.076964770000004</v>
       </c>
       <c r="C27" s="6">
-        <v>-49.418218719999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-49.546995160000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-71.148167659999999</v>
+        <v>-73.489324640000007</v>
       </c>
       <c r="C28" s="6">
-        <v>-51.06233443</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-51.193317739999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-71.408914379999999</v>
+        <v>-73.821622860000005</v>
       </c>
       <c r="C29" s="6">
-        <v>-52.489967970000002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-52.622764349999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-71.603900089999996</v>
+        <v>-74.097566240000006</v>
       </c>
       <c r="C30" s="6">
-        <v>-53.640615599999997</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-53.774887589999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-71.800155090000004</v>
+        <v>-74.38676298</v>
       </c>
       <c r="C31" s="6">
-        <v>-54.479416669999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-54.61396491</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-72.009803989999995</v>
+        <v>-74.618037220000005</v>
       </c>
       <c r="C32" s="6">
-        <v>-55.017806149999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.15135282</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-72.24265149</v>
+        <v>-74.939932659999997</v>
       </c>
       <c r="C33" s="6">
-        <v>-55.256465159999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.387617259999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-72.558470569999997</v>
+        <v>-75.282139909999998</v>
       </c>
       <c r="C34" s="6">
-        <v>-55.192006220000003</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.318991519999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-72.989332079999997</v>
+        <v>-75.772571650000003</v>
       </c>
       <c r="C35" s="6">
-        <v>-54.864078890000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-54.985567879999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="8">
-        <v>-49.026561787025003</v>
+        <v>-50.816524505890627</v>
       </c>
       <c r="C36" s="8">
-        <v>-35.132180516531243</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.221375927531248</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
     </row>
-    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
     </row>
   </sheetData>
@@ -3282,21 +3286,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C73779D-48E1-4396-BCEC-CC77B9A96BB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F94775C-2142-4275-87E7-127A4B3F5670}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.5703125" customWidth="1"/>
+    <col min="1" max="3" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -3307,7 +3311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -3318,373 +3322,373 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="6">
-        <v>6.6479016953999999</v>
+        <v>5.3375646118000004</v>
       </c>
       <c r="C4" s="7">
-        <v>-8.4250997040000009</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-8.3424564629999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="6">
-        <v>7.1046583332999997</v>
+        <v>3.3978625</v>
       </c>
       <c r="C5" s="6">
-        <v>-18.93440395</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-18.777869509999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
       <c r="B6" s="6">
-        <v>-2.926712974</v>
+        <v>5.5674684034000004</v>
       </c>
       <c r="C6" s="6">
-        <v>-6.5887610170000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-6.5031848160000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="6">
-        <v>-14.054845930000001</v>
+        <v>-13.537172590000001</v>
       </c>
       <c r="C7" s="6">
-        <v>-9.7081414230000007</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-9.7470649100000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="6">
-        <v>-19.05586533</v>
+        <v>-19.83186422</v>
       </c>
       <c r="C8" s="6">
-        <v>-13.98810675</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-14.10108906</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
       <c r="B9" s="6">
-        <v>-21.562719229999999</v>
+        <v>-23.69107455</v>
       </c>
       <c r="C9" s="6">
-        <v>-18.163567799999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-18.311611160000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
       <c r="B10" s="6">
-        <v>-24.50846623</v>
+        <v>-26.914938200000002</v>
       </c>
       <c r="C10" s="6">
-        <v>-21.174162429999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-21.32924062</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
       <c r="B11" s="6">
-        <v>-29.26293536</v>
+        <v>-32.255423810000003</v>
       </c>
       <c r="C11" s="6">
-        <v>-23.611543269999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-23.789757460000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
       <c r="B12" s="6">
-        <v>-33.452144599999997</v>
+        <v>-36.193182800000002</v>
       </c>
       <c r="C12" s="6">
-        <v>-25.245948890000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-25.435076939999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
       <c r="B13" s="6">
-        <v>-36.257550690000002</v>
+        <v>-38.412868670000002</v>
       </c>
       <c r="C13" s="6">
-        <v>-26.324832099999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-26.49993439</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
       <c r="B14" s="6">
-        <v>-38.687743159999997</v>
+        <v>-39.806424229999998</v>
       </c>
       <c r="C14" s="6">
-        <v>-27.1029667</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.253286039999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
       <c r="B15" s="6">
-        <v>-40.57952607</v>
+        <v>-41.173835609999998</v>
       </c>
       <c r="C15" s="6">
-        <v>-27.763705009999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-27.88923986</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
       <c r="B16" s="6">
-        <v>-43.304706379999999</v>
+        <v>-43.806296109999998</v>
       </c>
       <c r="C16" s="6">
-        <v>-28.626325300000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-28.740374060000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
       <c r="B17" s="6">
-        <v>-47.412468269999998</v>
+        <v>-47.875078430000002</v>
       </c>
       <c r="C17" s="6">
-        <v>-29.829543770000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-29.947605299999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
       <c r="B18" s="6">
-        <v>-51.459958409999999</v>
+        <v>-52.311473079999999</v>
       </c>
       <c r="C18" s="6">
-        <v>-31.411004590000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-31.540475489999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
       <c r="B19" s="6">
-        <v>-54.779237950000002</v>
+        <v>-56.34412116</v>
       </c>
       <c r="C19" s="6">
-        <v>-33.229500090000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-33.370618149999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
       <c r="B20" s="6">
-        <v>-57.657033689999999</v>
+        <v>-59.867190520000001</v>
       </c>
       <c r="C20" s="6">
-        <v>-35.198334799999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.350059170000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
       <c r="B21" s="6">
-        <v>-60.051196099999999</v>
+        <v>-62.880936679999998</v>
       </c>
       <c r="C21" s="6">
-        <v>-37.274791999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-37.43498262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
       <c r="B22" s="6">
-        <v>-61.971416550000001</v>
+        <v>-65.361396940000006</v>
       </c>
       <c r="C22" s="6">
-        <v>-39.409508690000003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-39.575345630000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
       <c r="B23" s="6">
-        <v>-63.46370709</v>
+        <v>-67.330193910000006</v>
       </c>
       <c r="C23" s="6">
-        <v>-41.543833069999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-41.712729410000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>-64.639361570000005</v>
+        <v>-68.757097520000002</v>
       </c>
       <c r="C24" s="6">
-        <v>-43.618617270000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-43.789159099999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-65.546315149999998</v>
+        <v>-69.771599120000005</v>
       </c>
       <c r="C25" s="6">
-        <v>-45.574980590000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-45.74685538</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-66.269236430000007</v>
+        <v>-70.410478620000006</v>
       </c>
       <c r="C26" s="6">
-        <v>-47.448015589999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-47.620851180000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-66.873256389999995</v>
+        <v>-70.858830580000003</v>
       </c>
       <c r="C27" s="6">
-        <v>-49.245376489999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-49.418218719999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-67.405144989999997</v>
+        <v>-71.148167659999999</v>
       </c>
       <c r="C28" s="6">
-        <v>-50.88986045</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-51.06233443</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
       <c r="B29" s="6">
-        <v>-67.899962639999998</v>
+        <v>-71.408914379999999</v>
       </c>
       <c r="C29" s="6">
-        <v>-52.317818180000003</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-52.489967970000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
       <c r="B30" s="6">
-        <v>-68.393121019999995</v>
+        <v>-71.603900089999996</v>
       </c>
       <c r="C30" s="6">
-        <v>-53.46845055</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-53.640615599999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
       <c r="B31" s="6">
-        <v>-68.919188009999999</v>
+        <v>-71.800155090000004</v>
       </c>
       <c r="C31" s="6">
-        <v>-54.307336859999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-54.479416669999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
       <c r="B32" s="6">
-        <v>-69.427228479999997</v>
+        <v>-72.009803989999995</v>
       </c>
       <c r="C32" s="6">
-        <v>-54.84603224</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.017806149999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
       <c r="B33" s="6">
-        <v>-69.967548239999999</v>
+        <v>-72.24265149</v>
       </c>
       <c r="C33" s="6">
-        <v>-55.085355589999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.256465159999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
       <c r="B34" s="6">
-        <v>-70.560267899999999</v>
+        <v>-72.558470569999997</v>
       </c>
       <c r="C34" s="6">
-        <v>-55.022050309999997</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-55.192006220000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
       <c r="B35" s="6">
-        <v>-71.285762520000006</v>
+        <v>-72.989332079999997</v>
       </c>
       <c r="C35" s="6">
-        <v>-54.69621807</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-54.864078890000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B36" s="8">
-        <v>-46.996314603915621</v>
+        <v>-49.026561787025003</v>
       </c>
       <c r="C36" s="8">
-        <v>-35.002318548249995</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>-35.132180516531243</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
     </row>
-    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
     </row>
   </sheetData>
@@ -3693,21 +3697,432 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C73779D-48E1-4396-BCEC-CC77B9A96BB8}">
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="3" width="19.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6">
+        <v>6.6479016953999999</v>
+      </c>
+      <c r="C4" s="7">
+        <v>-8.4250997040000009</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6">
+        <v>7.1046583332999997</v>
+      </c>
+      <c r="C5" s="6">
+        <v>-18.93440395</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6">
+        <v>-2.926712974</v>
+      </c>
+      <c r="C6" s="6">
+        <v>-6.5887610170000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6">
+        <v>-14.054845930000001</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-9.7081414230000007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6">
+        <v>-19.05586533</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-13.98810675</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6">
+        <v>-21.562719229999999</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-18.163567799999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6">
+        <v>-24.50846623</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-21.174162429999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6">
+        <v>-29.26293536</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-23.611543269999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6">
+        <v>-33.452144599999997</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-25.245948890000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6">
+        <v>-36.257550690000002</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-26.324832099999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6">
+        <v>-38.687743159999997</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-27.1029667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6">
+        <v>-40.57952607</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-27.763705009999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6">
+        <v>-43.304706379999999</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-28.626325300000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="5">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6">
+        <v>-47.412468269999998</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-29.829543770000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6">
+        <v>-51.459958409999999</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-31.411004590000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="5">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6">
+        <v>-54.779237950000002</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-33.229500090000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6">
+        <v>-57.657033689999999</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-35.198334799999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6">
+        <v>-60.051196099999999</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-37.274791999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="5">
+        <v>17</v>
+      </c>
+      <c r="B22" s="6">
+        <v>-61.971416550000001</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-39.409508690000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="5">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6">
+        <v>-63.46370709</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-41.543833069999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="5">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6">
+        <v>-64.639361570000005</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-43.618617270000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="5">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6">
+        <v>-65.546315149999998</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-45.574980590000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="5">
+        <v>21</v>
+      </c>
+      <c r="B26" s="6">
+        <v>-66.269236430000007</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-47.448015589999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="5">
+        <v>22</v>
+      </c>
+      <c r="B27" s="6">
+        <v>-66.873256389999995</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-49.245376489999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="5">
+        <v>23</v>
+      </c>
+      <c r="B28" s="6">
+        <v>-67.405144989999997</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-50.88986045</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6">
+        <v>-67.899962639999998</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-52.317818180000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="5">
+        <v>25</v>
+      </c>
+      <c r="B30" s="6">
+        <v>-68.393121019999995</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-53.46845055</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="5">
+        <v>26</v>
+      </c>
+      <c r="B31" s="6">
+        <v>-68.919188009999999</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-54.307336859999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="5">
+        <v>27</v>
+      </c>
+      <c r="B32" s="6">
+        <v>-69.427228479999997</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-54.84603224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="5">
+        <v>28</v>
+      </c>
+      <c r="B33" s="6">
+        <v>-69.967548239999999</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-55.085355589999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="5">
+        <v>29</v>
+      </c>
+      <c r="B34" s="6">
+        <v>-70.560267899999999</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-55.022050309999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="5">
+        <v>30</v>
+      </c>
+      <c r="B35" s="6">
+        <v>-71.285762520000006</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-54.69621807</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="8">
+        <v>-46.996314603915621</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-35.002318548249995</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="9"/>
+    </row>
+    <row r="39" spans="1:3" ht="66" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F39390C-8944-4BA3-A374-C71CF55A3914}">
   <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="19.7109375" customWidth="1"/>
+    <col min="1" max="3" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -3718,7 +4133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -3729,7 +4144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -3740,7 +4155,7 @@
         <v>-8.4643284360000006</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -3751,7 +4166,7 @@
         <v>-18.986706460000001</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -3762,7 +4177,7 @@
         <v>-6.606153613</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
@@ -3773,7 +4188,7 @@
         <v>-9.6725825039999993</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
@@ -3784,7 +4199,7 @@
         <v>-13.90377076</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>4</v>
       </c>
@@ -3795,7 +4210,7 @@
         <v>-18.05126491</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>5</v>
       </c>
@@ -3806,7 +4221,7 @@
         <v>-21.058171550000001</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>6</v>
       </c>
@@ -3817,7 +4232,7 @@
         <v>-23.482340529999998</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>7</v>
       </c>
@@ -3828,7 +4243,7 @@
         <v>-25.112373340000001</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>8</v>
       </c>
@@ -3839,7 +4254,7 @@
         <v>-26.207170059999999</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>9</v>
       </c>
@@ -3850,7 +4265,7 @@
         <v>-27.01171896</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>10</v>
       </c>
@@ -3861,7 +4276,7 @@
         <v>-27.699147780000001</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>11</v>
       </c>
@@ -3872,7 +4287,7 @@
         <v>-28.582440519999999</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>12</v>
       </c>
@@ -3883,7 +4298,7 @@
         <v>-29.797805400000001</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>13</v>
       </c>
@@ -3894,7 +4309,7 @@
         <v>-31.38552271</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>14</v>
       </c>
@@ -3905,7 +4320,7 @@
         <v>-33.206359569999996</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>15</v>
       </c>
@@ -3916,7 +4331,7 @@
         <v>-35.175185190000001</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>16</v>
       </c>
@@ -3927,7 +4342,7 @@
         <v>-37.250174440000002</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>17</v>
       </c>
@@ -3938,7 +4353,7 @@
         <v>-39.383293340000002</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>18</v>
       </c>
@@ -3949,7 +4364,7 @@
         <v>-41.514898170000002</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>19</v>
       </c>
@@ -3960,7 +4375,7 @@
         <v>-43.58589877</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>20</v>
       </c>
@@ -3971,7 +4386,7 @@
         <v>-45.536655600000003</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>21</v>
       </c>
@@ -3982,7 +4397,7 @@
         <v>-47.402761550000001</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>22</v>
       </c>
@@ -3993,7 +4408,7 @@
         <v>-49.193163900000002</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>23</v>
       </c>
@@ -4004,7 +4419,7 @@
         <v>-50.831508980000002</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>24</v>
       </c>
@@ -4015,7 +4430,7 @@
         <v>-52.254304140000002</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>25</v>
       </c>
@@ -4026,7 +4441,7 @@
         <v>-53.401048920000001</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>26</v>
       </c>
@@ -4037,7 +4452,7 @@
         <v>-54.237701129999998</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>27</v>
       </c>
@@ -4048,7 +4463,7 @@
         <v>-54.776711149999997</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>28</v>
       </c>
@@ -4059,7 +4474,7 @@
         <v>-55.018984750000001</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>29</v>
       </c>
@@ -4070,7 +4485,7 @@
         <v>-54.961556510000001</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30</v>
       </c>
@@ -4081,7 +4496,7 @@
         <v>-54.64476792</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
@@ -4092,12 +4507,12 @@
         <v>-34.949889736343749</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
         <v>10</v>
       </c>
@@ -4114,28 +4529,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25262A5-84B2-4BF6-AF4E-DBAA1AC8379B}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="H31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="31" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H31" s="1"/>
     </row>
   </sheetData>
